--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/pre LAM_HRM-2031-0140/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/pre LAM_HRM-2031-0140/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,17 +434,17 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -454,28 +454,23 @@
           <t>Unit 7</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Trace 1</t>
-        </is>
-      </c>
       <c r="C2" t="n">
-        <v>16.5287</v>
+        <v>16.67457</v>
       </c>
       <c r="D2" t="n">
-        <v>15.76288</v>
+        <v>16.58766</v>
       </c>
       <c r="E2" t="n">
-        <v>16.23442</v>
+        <v>16.65099</v>
       </c>
       <c r="F2" t="n">
-        <v>21.80804</v>
+        <v>42.69709</v>
       </c>
       <c r="G2" t="n">
-        <v>22.16612</v>
+        <v>0.05004</v>
       </c>
       <c r="H2" t="n">
-        <v>33.92684</v>
+        <v>1.83256</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +480,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.94418</v>
+        <v>16.98886</v>
       </c>
       <c r="D3" t="n">
-        <v>15.84585</v>
+        <v>16.41935</v>
       </c>
       <c r="E3" t="n">
-        <v>15.9066</v>
+        <v>16.46595</v>
       </c>
       <c r="F3" t="n">
-        <v>21.70049</v>
+        <v>41.96781</v>
       </c>
       <c r="G3" t="n">
-        <v>21.81295</v>
+        <v>0.05077</v>
       </c>
       <c r="H3" t="n">
-        <v>34.48419</v>
+        <v>1.8143</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +505,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.98935</v>
+        <v>17.01421</v>
       </c>
       <c r="D4" t="n">
-        <v>16.33627</v>
+        <v>16.56477</v>
       </c>
       <c r="E4" t="n">
-        <v>16.37978</v>
+        <v>16.7931</v>
       </c>
       <c r="F4" t="n">
-        <v>21.79299</v>
+        <v>43.02768</v>
       </c>
       <c r="G4" t="n">
-        <v>22.0195</v>
+        <v>0.05114</v>
       </c>
       <c r="H4" t="n">
-        <v>34.60626</v>
+        <v>1.84328</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +530,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.81062</v>
+        <v>16.867</v>
       </c>
       <c r="D5" t="n">
-        <v>15.6763</v>
+        <v>16.43942</v>
       </c>
       <c r="E5" t="n">
-        <v>16.68848</v>
+        <v>16.83871</v>
       </c>
       <c r="F5" t="n">
-        <v>21.47574</v>
+        <v>41.9983</v>
       </c>
       <c r="G5" t="n">
-        <v>21.34896</v>
+        <v>0.05003</v>
       </c>
       <c r="H5" t="n">
-        <v>34.14323</v>
+        <v>1.79171</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +555,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.89788</v>
+        <v>16.84812</v>
       </c>
       <c r="D6" t="n">
-        <v>15.70525</v>
+        <v>16.51495</v>
       </c>
       <c r="E6" t="n">
-        <v>16.52761</v>
+        <v>16.77547</v>
       </c>
       <c r="F6" t="n">
-        <v>22.14404</v>
+        <v>41.74283</v>
       </c>
       <c r="G6" t="n">
-        <v>22.05356</v>
+        <v>0.05</v>
       </c>
       <c r="H6" t="n">
-        <v>34.29206</v>
+        <v>1.84423</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +580,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.98158</v>
+        <v>16.57584</v>
       </c>
       <c r="D7" t="n">
-        <v>15.70296</v>
+        <v>16.47505</v>
       </c>
       <c r="E7" t="n">
-        <v>16.47628</v>
+        <v>16.48594</v>
       </c>
       <c r="F7" t="n">
-        <v>21.37886</v>
+        <v>42.5624</v>
       </c>
       <c r="G7" t="n">
-        <v>21.85844</v>
+        <v>0.05123</v>
       </c>
       <c r="H7" t="n">
-        <v>34.0382</v>
+        <v>1.82904</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +605,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.603</v>
+        <v>16.89854</v>
       </c>
       <c r="D8" t="n">
-        <v>15.98192</v>
+        <v>16.227</v>
       </c>
       <c r="E8" t="n">
-        <v>16.11938</v>
+        <v>16.67952</v>
       </c>
       <c r="F8" t="n">
-        <v>21.96374</v>
+        <v>42.90945</v>
       </c>
       <c r="G8" t="n">
-        <v>21.55981</v>
+        <v>0.05072</v>
       </c>
       <c r="H8" t="n">
-        <v>33.75688</v>
+        <v>1.82652</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +630,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.67208</v>
+        <v>16.87623</v>
       </c>
       <c r="D9" t="n">
-        <v>15.81183</v>
+        <v>16.61542</v>
       </c>
       <c r="E9" t="n">
-        <v>16.67613</v>
+        <v>16.77496</v>
       </c>
       <c r="F9" t="n">
-        <v>21.36748</v>
+        <v>42.07304</v>
       </c>
       <c r="G9" t="n">
-        <v>21.77768</v>
+        <v>0.04988</v>
       </c>
       <c r="H9" t="n">
-        <v>34.5502</v>
+        <v>1.80382</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +655,284 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.9298</v>
+        <v>16.83784</v>
       </c>
       <c r="D10" t="n">
-        <v>16.22366</v>
+        <v>16.56192</v>
       </c>
       <c r="E10" t="n">
-        <v>16.45916</v>
+        <v>16.82983</v>
       </c>
       <c r="F10" t="n">
-        <v>21.45951</v>
+        <v>43.13063</v>
       </c>
       <c r="G10" t="n">
-        <v>21.58472</v>
+        <v>0.05015</v>
       </c>
       <c r="H10" t="n">
-        <v>34.84545</v>
+        <v>1.7674</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>16.834</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16.56169</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.7548</v>
+      </c>
+      <c r="F12" t="n">
+        <v>43.24561</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0517</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.81998</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>16.89359</v>
+      </c>
+      <c r="D13" t="n">
+        <v>16.71851</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.82622</v>
+      </c>
+      <c r="F13" t="n">
+        <v>42.79066</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.04961</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.85428</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>16.66755</v>
+      </c>
+      <c r="D14" t="n">
+        <v>16.20939</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.58127</v>
+      </c>
+      <c r="F14" t="n">
+        <v>43.01279</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0497</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.8364</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>17.09726</v>
+      </c>
+      <c r="D15" t="n">
+        <v>16.74021</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.74437</v>
+      </c>
+      <c r="F15" t="n">
+        <v>43.22585</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.04969</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.8307</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>16.61628</v>
+      </c>
+      <c r="D16" t="n">
+        <v>16.50646</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.59622</v>
+      </c>
+      <c r="F16" t="n">
+        <v>42.26218</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05058</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.79104</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>16.95805</v>
+      </c>
+      <c r="D17" t="n">
+        <v>16.36948</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.47895</v>
+      </c>
+      <c r="F17" t="n">
+        <v>42.43801</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05004</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.8529</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>16.86622</v>
+      </c>
+      <c r="D18" t="n">
+        <v>16.49768</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.53491</v>
+      </c>
+      <c r="F18" t="n">
+        <v>43.09403</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05134</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.8288</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>17.01035</v>
+      </c>
+      <c r="D19" t="n">
+        <v>16.3884</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.56874</v>
+      </c>
+      <c r="F19" t="n">
+        <v>43.2382</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05113</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.83062</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>16.97271</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16.63267</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.8113</v>
+      </c>
+      <c r="F20" t="n">
+        <v>41.06061</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05098</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.8183</v>
       </c>
     </row>
   </sheetData>
